--- a/backend/assets/template_fiche_provision.xlsx
+++ b/backend/assets/template_fiche_provision.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geralddurand-desgranges/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geralddurand-desgranges/Desktop/Fiches de provision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99414CFD-433C-9348-AF03-D11A63E1CCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBF81701-F99D-8B4D-BC22-DFCA928ED2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiche Provision VO" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>FICHE PROVISION PRÉPA VO YPOCAMP</t>
   </si>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t xml:space="preserve">                           PREPARATION ESTHETIQUE</t>
-  </si>
-  <si>
-    <t>OUI</t>
   </si>
   <si>
     <t xml:space="preserve"> PREPA MÉCANIQUE</t>
@@ -419,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -538,13 +535,16 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -932,22 +932,22 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
     </row>
     <row r="4" spans="1:6" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
@@ -987,13 +987,13 @@
       <c r="A8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
       <c r="D8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
     </row>
     <row r="9" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -1044,11 +1044,11 @@
       <c r="D12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="44">
         <f ca="1">TODAY()</f>
-        <v>46156</v>
-      </c>
-      <c r="F12" s="46"/>
+        <v>46170</v>
+      </c>
+      <c r="F12" s="44"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="39" t="s">
@@ -1069,11 +1069,11 @@
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
       <c r="D14" s="6" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E14" s="22">
         <f>IF(D14="OUI",230,0)</f>
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="F14" s="22"/>
     </row>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -1097,26 +1097,26 @@
     </row>
     <row r="17" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="8"/>
       <c r="D17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="38" t="s">
         <v>17</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>18</v>
       </c>
       <c r="F17" s="38"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="35"/>
       <c r="C18" s="2"/>
       <c r="D18" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" s="36">
         <f>IF(D18="OUI",80,0)</f>
@@ -1126,12 +1126,12 @@
     </row>
     <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="33"/>
       <c r="C19" s="4"/>
       <c r="D19" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" s="34">
         <f>IF(D19="OUI",150,0)</f>
@@ -1141,12 +1141,12 @@
     </row>
     <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" s="35"/>
       <c r="C20" s="2"/>
       <c r="D20" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" s="36">
         <f>IF(D20="OUI",350,0)</f>
@@ -1156,12 +1156,12 @@
     </row>
     <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" s="33"/>
       <c r="C21" s="4"/>
       <c r="D21" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" s="34">
         <f>IF(D21="OUI",600,0)</f>
@@ -1171,12 +1171,12 @@
     </row>
     <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" s="35"/>
       <c r="C22" s="2"/>
       <c r="D22" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" s="36">
         <f>IF(D22="OUI",850,0)</f>
@@ -1186,27 +1186,27 @@
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="33"/>
       <c r="C23" s="4"/>
       <c r="D23" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" s="34">
-        <f>IF(D23="OUI, 1",400,IF(D23="OUI, 2",800,0))</f>
+        <f>IF(D23="NON",0,IF(OR(D23=1,D23="1"),400,IF(OR(D23=2,D23="2"),800,0)))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="34"/>
+      <c r="F23" s="47"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="35"/>
       <c r="C24" s="2"/>
       <c r="D24" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24" s="36">
         <f>IF(D24="OUI",180,0)</f>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="37"/>
       <c r="C25" s="37"/>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -1249,13 +1249,13 @@
     </row>
     <row r="28" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" s="32"/>
       <c r="C28" s="32"/>
       <c r="D28" s="32"/>
       <c r="E28" s="32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F28" s="32"/>
     </row>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="36" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -1327,13 +1327,13 @@
     </row>
     <row r="37" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
       <c r="D37" s="32"/>
       <c r="E37" s="32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F37" s="32"/>
     </row>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="52" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
@@ -1461,13 +1461,13 @@
     </row>
     <row r="53" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B53" s="32"/>
       <c r="C53" s="32"/>
       <c r="D53" s="32"/>
       <c r="E53" s="32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F53" s="32"/>
     </row>
@@ -1505,7 +1505,7 @@
     </row>
     <row r="58" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
@@ -1525,14 +1525,14 @@
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B60" s="24"/>
       <c r="C60" s="24"/>
       <c r="D60" s="3"/>
       <c r="E60" s="25">
         <f>E13+E14+E18+E19+E20+E21+E22+E23+E24+E25+SUM(E29:E34)+SUM(E38:E51)+SUM(E54:E57)+E58</f>
-        <v>1655</v>
+        <v>1425</v>
       </c>
       <c r="F60" s="25"/>
     </row>
@@ -1546,14 +1546,14 @@
     </row>
     <row r="62" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
       <c r="D62" s="14"/>
       <c r="E62" s="20">
         <f>E10+E60</f>
-        <v>1655</v>
+        <v>1425</v>
       </c>
       <c r="F62" s="20"/>
     </row>
@@ -1709,8 +1709,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation type="list" sqref="D23" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"NON,OUI,1,OUI,2"</formula1>
-      <formula2>0</formula2>
+      <formula1>"NON,1,2"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/backend/assets/template_fiche_provision.xlsx
+++ b/backend/assets/template_fiche_provision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geralddurand-desgranges/Desktop/Fiches de provision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBF81701-F99D-8B4D-BC22-DFCA928ED2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2495AB59-7ECD-D64A-81D5-53612AC59D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17220" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiche Provision VO" sheetId="1" r:id="rId1"/>
@@ -460,18 +460,84 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -479,79 +545,405 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC0392B"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A6B35"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD4EDDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -932,22 +1324,22 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
     </row>
     <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="4" spans="1:6" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
@@ -974,124 +1366,124 @@
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
       <c r="D8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
     </row>
     <row r="10" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
       <c r="D10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="23">
         <v>0</v>
       </c>
-      <c r="F10" s="43"/>
+      <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
       <c r="D11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="23">
         <v>0</v>
       </c>
-      <c r="F11" s="43"/>
+      <c r="F11" s="23"/>
     </row>
     <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="24">
         <f ca="1">TODAY()</f>
         <v>46170</v>
       </c>
-      <c r="F12" s="44"/>
+      <c r="F12" s="24"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="40">
+      <c r="E13" s="26">
         <v>1025</v>
       </c>
-      <c r="F13" s="40"/>
+      <c r="F13" s="26"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="27">
         <f>IF(D14="OUI",230,0)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="22"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:6" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="41"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
     </row>
     <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
@@ -1104,130 +1496,130 @@
       <c r="D17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="38"/>
+      <c r="F17" s="29"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="35"/>
+      <c r="B18" s="30"/>
       <c r="C18" s="2"/>
       <c r="D18" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="31">
         <f>IF(D18="OUI",80,0)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="36"/>
+      <c r="F18" s="31"/>
     </row>
     <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="33"/>
+      <c r="B19" s="32"/>
       <c r="C19" s="4"/>
       <c r="D19" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="33">
         <f>IF(D19="OUI",150,0)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="34"/>
+      <c r="F19" s="33"/>
     </row>
     <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="35"/>
+      <c r="B20" s="30"/>
       <c r="C20" s="2"/>
       <c r="D20" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="31">
         <f>IF(D20="OUI",350,0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="36"/>
+      <c r="F20" s="31"/>
     </row>
     <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="33"/>
+      <c r="B21" s="32"/>
       <c r="C21" s="4"/>
       <c r="D21" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="33">
         <f>IF(D21="OUI",600,0)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="34"/>
+      <c r="F21" s="33"/>
     </row>
     <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="35"/>
+      <c r="B22" s="30"/>
       <c r="C22" s="2"/>
       <c r="D22" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="31">
         <f>IF(D22="OUI",850,0)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="36"/>
+      <c r="F22" s="31"/>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="33"/>
+      <c r="B23" s="32"/>
       <c r="C23" s="4"/>
       <c r="D23" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="33">
         <f>IF(D23="NON",0,IF(OR(D23=1,D23="1"),400,IF(OR(D23=2,D23="2"),800,0)))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="47"/>
+      <c r="F23" s="34"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="35" t="s">
+      <c r="A24" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="35"/>
+      <c r="B24" s="30"/>
       <c r="C24" s="2"/>
       <c r="D24" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="36">
+      <c r="E24" s="31">
         <f>IF(D24="OUI",180,0)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="36"/>
+      <c r="F24" s="31"/>
     </row>
     <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
       <c r="D25" s="13">
         <v>0</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="33">
         <f>IF(D25="OUI",180,0)</f>
         <v>0</v>
       </c>
-      <c r="F25" s="34"/>
+      <c r="F25" s="33"/>
     </row>
     <row r="26" spans="1:6" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
@@ -1238,74 +1630,74 @@
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32" t="s">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="F28" s="32"/>
+      <c r="F28" s="36"/>
     </row>
     <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
     </row>
     <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="26"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
+      <c r="A30" s="39"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
     </row>
     <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
     </row>
     <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="26"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="A32" s="39"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="26"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
+      <c r="A34" s="39"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
     </row>
     <row r="35" spans="1:6" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
@@ -1316,225 +1708,225 @@
       <c r="F35" s="2"/>
     </row>
     <row r="36" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
     </row>
     <row r="37" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32" t="s">
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="F37" s="32"/>
+      <c r="F37" s="36"/>
     </row>
     <row r="38" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
     </row>
     <row r="39" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="26"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
+      <c r="A39" s="39"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
     </row>
     <row r="40" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
+      <c r="A40" s="37"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
     </row>
     <row r="41" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="26"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
+      <c r="A41" s="39"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
     </row>
     <row r="42" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
+      <c r="A42" s="37"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
     </row>
     <row r="43" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="26"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
+      <c r="A43" s="39"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
     </row>
     <row r="44" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
+      <c r="A44" s="37"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
     </row>
     <row r="45" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="26"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
+      <c r="A45" s="39"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
     </row>
     <row r="46" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
+      <c r="A46" s="37"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
     </row>
     <row r="47" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="26"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
+      <c r="A47" s="39"/>
+      <c r="B47" s="39"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="39"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
     </row>
     <row r="48" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
+      <c r="A48" s="37"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="38"/>
     </row>
     <row r="49" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="26"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
+      <c r="A49" s="39"/>
+      <c r="B49" s="39"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
     </row>
     <row r="50" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
+      <c r="A50" s="37"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
     </row>
     <row r="51" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="26"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
+      <c r="A51" s="39"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
     </row>
     <row r="52" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
     </row>
     <row r="53" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="32" t="s">
+      <c r="A53" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B53" s="32"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32" t="s">
+      <c r="B53" s="36"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="F53" s="32"/>
+      <c r="F53" s="36"/>
     </row>
     <row r="54" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="28"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
+      <c r="A54" s="37"/>
+      <c r="B54" s="37"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
     </row>
     <row r="55" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="26"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
+      <c r="A55" s="39"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="39"/>
+      <c r="D55" s="39"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
     </row>
     <row r="56" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="28"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
+      <c r="A56" s="37"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
     </row>
     <row r="57" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="31"/>
+      <c r="A57" s="41"/>
+      <c r="B57" s="41"/>
+      <c r="C57" s="41"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
     </row>
     <row r="58" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="22">
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="27">
         <v>400</v>
       </c>
-      <c r="F58" s="22"/>
+      <c r="F58" s="27"/>
     </row>
     <row r="59" spans="1:6" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="23"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
+      <c r="A59" s="45"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="45"/>
+      <c r="D59" s="45"/>
+      <c r="E59" s="45"/>
+      <c r="F59" s="45"/>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="24" t="s">
+      <c r="A60" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B60" s="24"/>
-      <c r="C60" s="24"/>
+      <c r="B60" s="46"/>
+      <c r="C60" s="46"/>
       <c r="D60" s="3"/>
-      <c r="E60" s="25">
+      <c r="E60" s="47">
         <f>E13+E14+E18+E19+E20+E21+E22+E23+E24+E25+SUM(E29:E34)+SUM(E38:E51)+SUM(E54:E57)+E58</f>
         <v>1425</v>
       </c>
-      <c r="F60" s="25"/>
+      <c r="F60" s="47"/>
     </row>
     <row r="61" spans="1:6" ht="3" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3"/>
@@ -1545,17 +1937,17 @@
       <c r="F61" s="3"/>
     </row>
     <row r="62" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="19" t="s">
+      <c r="A62" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
+      <c r="B62" s="43"/>
+      <c r="C62" s="43"/>
       <c r="D62" s="14"/>
-      <c r="E62" s="20">
+      <c r="E62" s="44">
         <f>E10+E60</f>
         <v>1425</v>
       </c>
-      <c r="F62" s="20"/>
+      <c r="F62" s="44"/>
     </row>
     <row r="63" spans="1:6" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
@@ -1587,98 +1979,6 @@
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="A2:F3"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="E57:F57"/>
     <mergeCell ref="A62:C62"/>
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="A58:D58"/>
@@ -1686,21 +1986,133 @@
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="E60:F60"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A2:F3"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E9:F9"/>
   </mergeCells>
   <conditionalFormatting sqref="D14">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="OUI">
+    <cfRule type="containsText" dxfId="15" priority="7" stopIfTrue="1" operator="containsText" text="NON">
+      <formula>NOT(ISERROR(SEARCH("NON",D14)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="OUI">
       <formula>NOT(ISERROR(SEARCH("OUI",D14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="NON">
-      <formula>NOT(ISERROR(SEARCH("NON",D14)))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19:D22 D24">
+    <cfRule type="expression" dxfId="13" priority="8">
+      <formula>OR(D24=1,D24="1",D24=2,D24="2")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D24">
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="OUI">
+  <conditionalFormatting sqref="D23">
+    <cfRule type="expression" dxfId="12" priority="4">
+      <formula>OR($D$23=1,$D$23="1",$D$23=2,$D$23="2")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19:D24">
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>OR(D19="OUI",D19=1,D19="1",D19=2,D19="2")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18">
+    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="OUI">
       <formula>NOT(ISERROR(SEARCH("OUI",D18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="NON">
-      <formula>NOT(ISERROR(SEARCH("NON",D18)))</formula>
+    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="OUI">
+      <formula>NOT(ISERROR(SEARCH("OUI",D18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19:D24">
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="NON">
+      <formula>NOT(ISERROR(SEARCH("NON",D19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
